--- a/Översikt LANDSKRONA.xlsx
+++ b/Översikt LANDSKRONA.xlsx
@@ -601,7 +601,7 @@
         <v>46256</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>45856</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>45153</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>

--- a/Översikt LANDSKRONA.xlsx
+++ b/Översikt LANDSKRONA.xlsx
@@ -601,7 +601,7 @@
         <v>46256</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 35536-2025</t>
+          <t>A 36713-2023</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45856</v>
+        <v>45153</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>0.7</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -762,7 +762,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 36713-2023</t>
+          <t>A 35536-2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -776,10 +776,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45153</v>
+        <v>45856</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.7</v>
+        <v>4</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>

--- a/Översikt LANDSKRONA.xlsx
+++ b/Översikt LANDSKRONA.xlsx
@@ -601,7 +601,7 @@
         <v>46256</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 36713-2023</t>
+          <t>A 35536-2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45153</v>
+        <v>45856</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.7</v>
+        <v>4</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -762,7 +762,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 35536-2025</t>
+          <t>A 36713-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -776,10 +776,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45856</v>
+        <v>45153</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>0.7</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>

--- a/Översikt LANDSKRONA.xlsx
+++ b/Översikt LANDSKRONA.xlsx
@@ -601,7 +601,7 @@
         <v>46256</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>45856</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>45153</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>

--- a/Översikt LANDSKRONA.xlsx
+++ b/Översikt LANDSKRONA.xlsx
@@ -601,7 +601,7 @@
         <v>46256</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 35536-2025</t>
+          <t>A 36713-2023</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45856</v>
+        <v>45153</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>0.7</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -762,7 +762,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 36713-2023</t>
+          <t>A 35536-2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -776,10 +776,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45153</v>
+        <v>45856</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.7</v>
+        <v>4</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>

--- a/Översikt LANDSKRONA.xlsx
+++ b/Översikt LANDSKRONA.xlsx
@@ -601,7 +601,7 @@
         <v>46256</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>45153</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>45856</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>

--- a/Översikt LANDSKRONA.xlsx
+++ b/Översikt LANDSKRONA.xlsx
@@ -601,7 +601,7 @@
         <v>46256</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>45153</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>45856</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>

--- a/Översikt LANDSKRONA.xlsx
+++ b/Översikt LANDSKRONA.xlsx
@@ -601,7 +601,7 @@
         <v>46256</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>45153</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>45856</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>

--- a/Översikt LANDSKRONA.xlsx
+++ b/Översikt LANDSKRONA.xlsx
@@ -601,7 +601,7 @@
         <v>46256</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>45153</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>45856</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>

--- a/Översikt LANDSKRONA.xlsx
+++ b/Översikt LANDSKRONA.xlsx
@@ -601,7 +601,7 @@
         <v>46256</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 36713-2023</t>
+          <t>A 35536-2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45153</v>
+        <v>45856</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.7</v>
+        <v>4</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -762,7 +762,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 35536-2025</t>
+          <t>A 36713-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -776,10 +776,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45856</v>
+        <v>45153</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>0.7</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>

--- a/Översikt LANDSKRONA.xlsx
+++ b/Översikt LANDSKRONA.xlsx
@@ -601,7 +601,7 @@
         <v>46256</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>45856</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>45153</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>

--- a/Översikt LANDSKRONA.xlsx
+++ b/Översikt LANDSKRONA.xlsx
@@ -601,7 +601,7 @@
         <v>46256</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>45856</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>45153</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>

--- a/Översikt LANDSKRONA.xlsx
+++ b/Översikt LANDSKRONA.xlsx
@@ -601,7 +601,7 @@
         <v>46256</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>45856</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>45153</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>

--- a/Översikt LANDSKRONA.xlsx
+++ b/Översikt LANDSKRONA.xlsx
@@ -601,7 +601,7 @@
         <v>46256</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>45856</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>45153</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>

--- a/Översikt LANDSKRONA.xlsx
+++ b/Översikt LANDSKRONA.xlsx
@@ -601,7 +601,7 @@
         <v>46256</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 35536-2025</t>
+          <t>A 36713-2023</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45856</v>
+        <v>45153</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>0.7</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -762,7 +762,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 36713-2023</t>
+          <t>A 35536-2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -776,10 +776,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45153</v>
+        <v>45856</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.7</v>
+        <v>4</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>

--- a/Översikt LANDSKRONA.xlsx
+++ b/Översikt LANDSKRONA.xlsx
@@ -601,7 +601,7 @@
         <v>46256</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 36713-2023</t>
+          <t>A 35536-2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45153</v>
+        <v>45856</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.7</v>
+        <v>4</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -762,7 +762,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 35536-2025</t>
+          <t>A 36713-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -776,10 +776,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45856</v>
+        <v>45153</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>0.7</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>

--- a/Översikt LANDSKRONA.xlsx
+++ b/Översikt LANDSKRONA.xlsx
@@ -601,7 +601,7 @@
         <v>46256</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 35536-2025</t>
+          <t>A 36713-2023</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45856</v>
+        <v>45153</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>0.7</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -762,7 +762,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 36713-2023</t>
+          <t>A 35536-2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -776,10 +776,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45153</v>
+        <v>45856</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.7</v>
+        <v>4</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>

--- a/Översikt LANDSKRONA.xlsx
+++ b/Översikt LANDSKRONA.xlsx
@@ -601,7 +601,7 @@
         <v>46256</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>45153</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>45856</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>

--- a/Översikt LANDSKRONA.xlsx
+++ b/Översikt LANDSKRONA.xlsx
@@ -601,7 +601,7 @@
         <v>46256</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>45153</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>45856</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>

--- a/Översikt LANDSKRONA.xlsx
+++ b/Översikt LANDSKRONA.xlsx
@@ -601,7 +601,7 @@
         <v>46256</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 36713-2023</t>
+          <t>A 35536-2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45153</v>
+        <v>45856</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.7</v>
+        <v>4</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -762,7 +762,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 35536-2025</t>
+          <t>A 36713-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -776,10 +776,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45856</v>
+        <v>45153</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>0.7</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>

--- a/Översikt LANDSKRONA.xlsx
+++ b/Översikt LANDSKRONA.xlsx
@@ -601,7 +601,7 @@
         <v>46256</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 35536-2025</t>
+          <t>A 36713-2023</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45856</v>
+        <v>45153</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>0.7</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -762,7 +762,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 36713-2023</t>
+          <t>A 35536-2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -776,10 +776,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45153</v>
+        <v>45856</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.7</v>
+        <v>4</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>

--- a/Översikt LANDSKRONA.xlsx
+++ b/Översikt LANDSKRONA.xlsx
@@ -601,7 +601,7 @@
         <v>46256</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>45153</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>45856</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>

--- a/Översikt LANDSKRONA.xlsx
+++ b/Översikt LANDSKRONA.xlsx
@@ -601,7 +601,7 @@
         <v>46256</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 36713-2023</t>
+          <t>A 35536-2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45153</v>
+        <v>45856</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.7</v>
+        <v>4</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -762,7 +762,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 35536-2025</t>
+          <t>A 36713-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -776,10 +776,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45856</v>
+        <v>45153</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>0.7</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>

--- a/Översikt LANDSKRONA.xlsx
+++ b/Översikt LANDSKRONA.xlsx
@@ -601,7 +601,7 @@
         <v>46256</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 35536-2025</t>
+          <t>A 36713-2023</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45856</v>
+        <v>45153</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>0.7</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -762,7 +762,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 36713-2023</t>
+          <t>A 35536-2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -776,10 +776,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45153</v>
+        <v>45856</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.7</v>
+        <v>4</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>

--- a/Översikt LANDSKRONA.xlsx
+++ b/Översikt LANDSKRONA.xlsx
@@ -601,7 +601,7 @@
         <v>46256</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>45153</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>45856</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>

--- a/Översikt LANDSKRONA.xlsx
+++ b/Översikt LANDSKRONA.xlsx
@@ -601,7 +601,7 @@
         <v>46256</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>45153</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>45856</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>

--- a/Översikt LANDSKRONA.xlsx
+++ b/Översikt LANDSKRONA.xlsx
@@ -601,7 +601,7 @@
         <v>46256</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 36713-2023</t>
+          <t>A 35536-2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45153</v>
+        <v>45856</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.7</v>
+        <v>4</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -762,7 +762,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 35536-2025</t>
+          <t>A 36713-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -776,10 +776,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45856</v>
+        <v>45153</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>0.7</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>

--- a/Översikt LANDSKRONA.xlsx
+++ b/Översikt LANDSKRONA.xlsx
@@ -601,7 +601,7 @@
         <v>46256</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>45856</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>45153</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>

--- a/Översikt LANDSKRONA.xlsx
+++ b/Översikt LANDSKRONA.xlsx
@@ -601,7 +601,7 @@
         <v>46256</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>45856</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>45153</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>

--- a/Översikt LANDSKRONA.xlsx
+++ b/Översikt LANDSKRONA.xlsx
@@ -601,7 +601,7 @@
         <v>46256</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>45856</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>45153</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>

--- a/Översikt LANDSKRONA.xlsx
+++ b/Översikt LANDSKRONA.xlsx
@@ -601,7 +601,7 @@
         <v>46256</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 35536-2025</t>
+          <t>A 36713-2023</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45856</v>
+        <v>45153</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>0.7</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -762,7 +762,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 36713-2023</t>
+          <t>A 35536-2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -776,10 +776,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45153</v>
+        <v>45856</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.7</v>
+        <v>4</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>

--- a/Översikt LANDSKRONA.xlsx
+++ b/Översikt LANDSKRONA.xlsx
@@ -601,7 +601,7 @@
         <v>46256</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>45153</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>45856</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>

--- a/Översikt LANDSKRONA.xlsx
+++ b/Översikt LANDSKRONA.xlsx
@@ -601,7 +601,7 @@
         <v>46256</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>45153</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>45856</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>

--- a/Översikt LANDSKRONA.xlsx
+++ b/Översikt LANDSKRONA.xlsx
@@ -601,7 +601,7 @@
         <v>46256</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>45153</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>45856</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>

--- a/Översikt LANDSKRONA.xlsx
+++ b/Översikt LANDSKRONA.xlsx
@@ -601,7 +601,7 @@
         <v>46256</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>45153</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>45856</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>

--- a/Översikt LANDSKRONA.xlsx
+++ b/Översikt LANDSKRONA.xlsx
@@ -601,7 +601,7 @@
         <v>46256</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 36713-2023</t>
+          <t>A 35536-2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45153</v>
+        <v>45856</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.7</v>
+        <v>4</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -762,7 +762,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 35536-2025</t>
+          <t>A 36713-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -776,10 +776,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45856</v>
+        <v>45153</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>0.7</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>

--- a/Översikt LANDSKRONA.xlsx
+++ b/Översikt LANDSKRONA.xlsx
@@ -601,7 +601,7 @@
         <v>46256</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>45856</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>45153</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>

--- a/Översikt LANDSKRONA.xlsx
+++ b/Översikt LANDSKRONA.xlsx
@@ -601,7 +601,7 @@
         <v>46256</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>45856</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>45153</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>

--- a/Översikt LANDSKRONA.xlsx
+++ b/Översikt LANDSKRONA.xlsx
@@ -601,7 +601,7 @@
         <v>46256</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>45856</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>45153</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>

--- a/Översikt LANDSKRONA.xlsx
+++ b/Översikt LANDSKRONA.xlsx
@@ -601,7 +601,7 @@
         <v>46256</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>45856</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>45153</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>

--- a/Översikt LANDSKRONA.xlsx
+++ b/Översikt LANDSKRONA.xlsx
@@ -601,7 +601,7 @@
         <v>46256</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 35536-2025</t>
+          <t>A 36713-2023</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45856</v>
+        <v>45153</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>0.7</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -762,7 +762,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 36713-2023</t>
+          <t>A 35536-2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -776,10 +776,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45153</v>
+        <v>45856</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.7</v>
+        <v>4</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>

--- a/Översikt LANDSKRONA.xlsx
+++ b/Översikt LANDSKRONA.xlsx
@@ -601,7 +601,7 @@
         <v>46256</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>45153</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>45856</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>

--- a/Översikt LANDSKRONA.xlsx
+++ b/Översikt LANDSKRONA.xlsx
@@ -601,7 +601,7 @@
         <v>46256</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 36713-2023</t>
+          <t>A 35536-2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45153</v>
+        <v>45856</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.7</v>
+        <v>4</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -762,7 +762,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 35536-2025</t>
+          <t>A 36713-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -776,10 +776,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45856</v>
+        <v>45153</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>0.7</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>

--- a/Översikt LANDSKRONA.xlsx
+++ b/Översikt LANDSKRONA.xlsx
@@ -601,7 +601,7 @@
         <v>46256</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 35536-2025</t>
+          <t>A 36713-2023</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45856</v>
+        <v>45153</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>0.7</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -762,7 +762,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 36713-2023</t>
+          <t>A 35536-2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -776,10 +776,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45153</v>
+        <v>45856</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.7</v>
+        <v>4</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
